--- a/assets/holdout_validation_FY24-25.xlsx
+++ b/assets/holdout_validation_FY24-25.xlsx
@@ -13,15 +13,20 @@
     <sheet name="Static - region monthly" sheetId="4" r:id="rId4"/>
     <sheet name="Static - per series" sheetId="5" r:id="rId5"/>
     <sheet name="Champions" sheetId="6" r:id="rId6"/>
-    <sheet name="Static - original engine" sheetId="7" r:id="rId7"/>
-    <sheet name="Static all SKUs - orig vs new" sheetId="8" r:id="rId8"/>
+    <sheet name="Rolling - by level &amp; lag" sheetId="7" r:id="rId7"/>
+    <sheet name="Rolling - region monthly" sheetId="8" r:id="rId8"/>
+    <sheet name="Rolling - all SKUs (lag 1-4)" sheetId="9" r:id="rId9"/>
+    <sheet name="Static - original engine" sheetId="10" r:id="rId10"/>
+    <sheet name="Static all SKUs - orig vs new" sheetId="11" r:id="rId11"/>
+    <sheet name="Models - static" sheetId="12" r:id="rId12"/>
+    <sheet name="Models - rolling lag 1-4" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="186">
   <si>
     <t>check</t>
   </si>
@@ -455,82 +460,130 @@
     <t>Moving Average</t>
   </si>
   <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>Naive</t>
+  </si>
+  <si>
+    <t>ARIMA</t>
+  </si>
+  <si>
+    <t>SARIMA</t>
+  </si>
+  <si>
+    <t>Exponential Smoothing</t>
+  </si>
+  <si>
+    <t>LightGBM</t>
+  </si>
+  <si>
     <t>Random Forest</t>
   </si>
   <si>
-    <t>Naive</t>
+    <t>Gradient Boosting</t>
+  </si>
+  <si>
+    <t>TSB</t>
+  </si>
+  <si>
+    <t>SBA</t>
+  </si>
+  <si>
+    <t>Trending</t>
+  </si>
+  <si>
+    <t>Erratic</t>
+  </si>
+  <si>
+    <t>Lumpy</t>
+  </si>
+  <si>
+    <t>Smooth</t>
+  </si>
+  <si>
+    <t>Seasonal</t>
+  </si>
+  <si>
+    <t>Seasonal + Trending</t>
+  </si>
+  <si>
+    <t>Intermittent</t>
+  </si>
+  <si>
+    <t>series</t>
+  </si>
+  <si>
+    <t>flat_forecasts</t>
+  </si>
+  <si>
+    <t>holdout_actual</t>
+  </si>
+  <si>
+    <t>lag</t>
+  </si>
+  <si>
+    <t>lag 1-4 wks</t>
+  </si>
+  <si>
+    <t>lag 5-8 wks</t>
+  </si>
+  <si>
+    <t>lag 9-12 wks</t>
+  </si>
+  <si>
+    <t>moving_avg_4w</t>
+  </si>
+  <si>
+    <t>Branch x Month (all SKUs)</t>
+  </si>
+  <si>
+    <t>South Region x Month (all SKUs)</t>
+  </si>
+  <si>
+    <t>South Region x Quarter (all SKUs)</t>
+  </si>
+  <si>
+    <t>engine</t>
+  </si>
+  <si>
+    <t>original</t>
+  </si>
+  <si>
+    <t>current</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Series</t>
+  </si>
+  <si>
+    <t>Volume covered %</t>
+  </si>
+  <si>
+    <t>SKU x Branch x Week WAPE %</t>
+  </si>
+  <si>
+    <t>SKU x Branch x Month WAPE %</t>
+  </si>
+  <si>
+    <t>Branch x Month WAPE %</t>
+  </si>
+  <si>
+    <t>South Region x Month WAPE %</t>
+  </si>
+  <si>
+    <t>vs champion, same series (SKU x Branch x Month, pts)</t>
+  </si>
+  <si>
+    <t>Champion (auto-selected)</t>
   </si>
   <si>
     <t>Seasonal Naive</t>
   </si>
   <si>
-    <t>ARIMA</t>
-  </si>
-  <si>
-    <t>SARIMA</t>
-  </si>
-  <si>
-    <t>Exponential Smoothing</t>
-  </si>
-  <si>
-    <t>LightGBM</t>
-  </si>
-  <si>
-    <t>Gradient Boosting</t>
-  </si>
-  <si>
-    <t>TSB</t>
-  </si>
-  <si>
-    <t>SBA</t>
-  </si>
-  <si>
-    <t>Trending</t>
-  </si>
-  <si>
-    <t>Erratic</t>
-  </si>
-  <si>
-    <t>Lumpy</t>
-  </si>
-  <si>
-    <t>Smooth</t>
-  </si>
-  <si>
-    <t>Seasonal</t>
-  </si>
-  <si>
-    <t>Seasonal + Trending</t>
-  </si>
-  <si>
-    <t>Intermittent</t>
-  </si>
-  <si>
-    <t>series</t>
-  </si>
-  <si>
-    <t>flat_forecasts</t>
-  </si>
-  <si>
-    <t>holdout_actual</t>
-  </si>
-  <si>
-    <t>engine</t>
-  </si>
-  <si>
-    <t>Branch x Month (all SKUs)</t>
-  </si>
-  <si>
-    <t>South Region x Month (all SKUs)</t>
-  </si>
-  <si>
-    <t>South Region x Quarter (all SKUs)</t>
-  </si>
-  <si>
-    <t>original</t>
-  </si>
-  <si>
-    <t>current</t>
+    <t>Croston</t>
   </si>
 </sst>
 </file>
@@ -1136,6 +1189,1491 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2">
+        <v>338772</v>
+      </c>
+      <c r="D2">
+        <v>343833</v>
+      </c>
+      <c r="E2">
+        <v>113</v>
+      </c>
+      <c r="F2">
+        <v>-13</v>
+      </c>
+      <c r="G2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3">
+        <v>338772</v>
+      </c>
+      <c r="D3">
+        <v>343833</v>
+      </c>
+      <c r="E3">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="F3">
+        <v>9.6</v>
+      </c>
+      <c r="G3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4">
+        <v>338772</v>
+      </c>
+      <c r="D4">
+        <v>343833</v>
+      </c>
+      <c r="E4">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="F4">
+        <v>21.9</v>
+      </c>
+      <c r="G4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5">
+        <v>338772</v>
+      </c>
+      <c r="D5">
+        <v>343833</v>
+      </c>
+      <c r="E5">
+        <v>54.6</v>
+      </c>
+      <c r="F5">
+        <v>45.4</v>
+      </c>
+      <c r="G5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6">
+        <v>338772</v>
+      </c>
+      <c r="D6">
+        <v>343833</v>
+      </c>
+      <c r="E6">
+        <v>50.7</v>
+      </c>
+      <c r="F6">
+        <v>49.3</v>
+      </c>
+      <c r="G6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7">
+        <v>338772</v>
+      </c>
+      <c r="D7">
+        <v>343833</v>
+      </c>
+      <c r="E7">
+        <v>31.7</v>
+      </c>
+      <c r="F7">
+        <v>68.3</v>
+      </c>
+      <c r="G7">
+        <v>1.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2">
+        <v>444274</v>
+      </c>
+      <c r="D2">
+        <v>343833</v>
+      </c>
+      <c r="E2">
+        <v>49.5</v>
+      </c>
+      <c r="F2">
+        <v>50.5</v>
+      </c>
+      <c r="G2">
+        <v>-22.6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3">
+        <v>444274</v>
+      </c>
+      <c r="D3">
+        <v>343833</v>
+      </c>
+      <c r="E3">
+        <v>42.7</v>
+      </c>
+      <c r="F3">
+        <v>57.3</v>
+      </c>
+      <c r="G3">
+        <v>-22.6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4">
+        <v>444274</v>
+      </c>
+      <c r="D4">
+        <v>343833</v>
+      </c>
+      <c r="E4">
+        <v>30.2</v>
+      </c>
+      <c r="F4">
+        <v>69.8</v>
+      </c>
+      <c r="G4">
+        <v>-22.6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5">
+        <v>444274</v>
+      </c>
+      <c r="D5">
+        <v>477061</v>
+      </c>
+      <c r="E5">
+        <v>41.9</v>
+      </c>
+      <c r="F5">
+        <v>58.1</v>
+      </c>
+      <c r="G5">
+        <v>7.4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6">
+        <v>444274</v>
+      </c>
+      <c r="D6">
+        <v>477061</v>
+      </c>
+      <c r="E6">
+        <v>38.8</v>
+      </c>
+      <c r="F6">
+        <v>61.2</v>
+      </c>
+      <c r="G6">
+        <v>7.4</v>
+      </c>
+      <c r="H6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7">
+        <v>444274</v>
+      </c>
+      <c r="D7">
+        <v>477061</v>
+      </c>
+      <c r="E7">
+        <v>31.5</v>
+      </c>
+      <c r="F7">
+        <v>68.5</v>
+      </c>
+      <c r="G7">
+        <v>7.4</v>
+      </c>
+      <c r="H7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2">
+        <v>205</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>93.5</v>
+      </c>
+      <c r="E2">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="F2">
+        <v>51.4</v>
+      </c>
+      <c r="G2">
+        <v>44.8</v>
+      </c>
+      <c r="H2">
+        <v>-32.5</v>
+      </c>
+      <c r="I2">
+        <v>-29.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3">
+        <v>205</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>111.1</v>
+      </c>
+      <c r="E3">
+        <v>81.3</v>
+      </c>
+      <c r="F3">
+        <v>49.5</v>
+      </c>
+      <c r="G3">
+        <v>43.9</v>
+      </c>
+      <c r="H3">
+        <v>-24.3</v>
+      </c>
+      <c r="I3">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4">
+        <v>205</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>109.1</v>
+      </c>
+      <c r="E4">
+        <v>82.2</v>
+      </c>
+      <c r="F4">
+        <v>58.9</v>
+      </c>
+      <c r="G4">
+        <v>55</v>
+      </c>
+      <c r="H4">
+        <v>-23.4</v>
+      </c>
+      <c r="I4">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5">
+        <v>205</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>118.6</v>
+      </c>
+      <c r="E5">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="F5">
+        <v>66.7</v>
+      </c>
+      <c r="G5">
+        <v>60.3</v>
+      </c>
+      <c r="H5">
+        <v>-10.5</v>
+      </c>
+      <c r="I5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6">
+        <v>205</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>132.1</v>
+      </c>
+      <c r="E6">
+        <v>101.8</v>
+      </c>
+      <c r="F6">
+        <v>60.4</v>
+      </c>
+      <c r="G6">
+        <v>50.7</v>
+      </c>
+      <c r="H6">
+        <v>-3.8</v>
+      </c>
+      <c r="I6">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7">
+        <v>205</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>134.6</v>
+      </c>
+      <c r="E7">
+        <v>105.6</v>
+      </c>
+      <c r="F7">
+        <v>60.9</v>
+      </c>
+      <c r="G7">
+        <v>46.8</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8">
+        <v>205</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>147.5</v>
+      </c>
+      <c r="E8">
+        <v>116.1</v>
+      </c>
+      <c r="F8">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G8">
+        <v>61.1</v>
+      </c>
+      <c r="H8">
+        <v>10.5</v>
+      </c>
+      <c r="I8">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9">
+        <v>188</v>
+      </c>
+      <c r="C9">
+        <v>56.9</v>
+      </c>
+      <c r="D9">
+        <v>158.5</v>
+      </c>
+      <c r="E9">
+        <v>124.5</v>
+      </c>
+      <c r="F9">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="G9">
+        <v>62.8</v>
+      </c>
+      <c r="H9">
+        <v>-12.7</v>
+      </c>
+      <c r="I9">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10">
+        <v>185</v>
+      </c>
+      <c r="C10">
+        <v>53.9</v>
+      </c>
+      <c r="D10">
+        <v>158.8</v>
+      </c>
+      <c r="E10">
+        <v>126.1</v>
+      </c>
+      <c r="F10">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="G10">
+        <v>69.2</v>
+      </c>
+      <c r="H10">
+        <v>-13.8</v>
+      </c>
+      <c r="I10">
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11">
+        <v>188</v>
+      </c>
+      <c r="C11">
+        <v>56.9</v>
+      </c>
+      <c r="D11">
+        <v>185.2</v>
+      </c>
+      <c r="E11">
+        <v>155.1</v>
+      </c>
+      <c r="F11">
+        <v>113.8</v>
+      </c>
+      <c r="G11">
+        <v>104.8</v>
+      </c>
+      <c r="H11">
+        <v>17.9</v>
+      </c>
+      <c r="I11">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12">
+        <v>126</v>
+      </c>
+      <c r="C12">
+        <v>12.7</v>
+      </c>
+      <c r="D12">
+        <v>228.3</v>
+      </c>
+      <c r="E12">
+        <v>188.1</v>
+      </c>
+      <c r="F12">
+        <v>125.4</v>
+      </c>
+      <c r="G12">
+        <v>117.4</v>
+      </c>
+      <c r="H12">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="I12">
+        <v>117.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13">
+        <v>35</v>
+      </c>
+      <c r="C13">
+        <v>10.5</v>
+      </c>
+      <c r="D13">
+        <v>267.9</v>
+      </c>
+      <c r="E13">
+        <v>228.6</v>
+      </c>
+      <c r="F13">
+        <v>163.3</v>
+      </c>
+      <c r="G13">
+        <v>160.3</v>
+      </c>
+      <c r="H13">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="I13">
+        <v>158.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14">
+        <v>126</v>
+      </c>
+      <c r="C14">
+        <v>12.7</v>
+      </c>
+      <c r="D14">
+        <v>379.2</v>
+      </c>
+      <c r="E14">
+        <v>341.7</v>
+      </c>
+      <c r="F14">
+        <v>267.1</v>
+      </c>
+      <c r="G14">
+        <v>263.3</v>
+      </c>
+      <c r="H14">
+        <v>218.7</v>
+      </c>
+      <c r="I14">
+        <v>263.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15">
+        <v>155</v>
+      </c>
+      <c r="C15">
+        <v>29.2</v>
+      </c>
+      <c r="D15">
+        <v>378.8</v>
+      </c>
+      <c r="E15">
+        <v>348</v>
+      </c>
+      <c r="F15">
+        <v>271.2</v>
+      </c>
+      <c r="G15">
+        <v>271.2</v>
+      </c>
+      <c r="H15">
+        <v>162.7</v>
+      </c>
+      <c r="I15">
+        <v>271.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16">
+        <v>126</v>
+      </c>
+      <c r="C16">
+        <v>12.7</v>
+      </c>
+      <c r="D16">
+        <v>395.2</v>
+      </c>
+      <c r="E16">
+        <v>356.6</v>
+      </c>
+      <c r="F16">
+        <v>284.3</v>
+      </c>
+      <c r="G16">
+        <v>282.4</v>
+      </c>
+      <c r="H16">
+        <v>233.6</v>
+      </c>
+      <c r="I16">
+        <v>282.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17">
+        <v>155</v>
+      </c>
+      <c r="C17">
+        <v>29.2</v>
+      </c>
+      <c r="D17">
+        <v>428.3</v>
+      </c>
+      <c r="E17">
+        <v>389.9</v>
+      </c>
+      <c r="F17">
+        <v>343.2</v>
+      </c>
+      <c r="G17">
+        <v>343.2</v>
+      </c>
+      <c r="H17">
+        <v>204.6</v>
+      </c>
+      <c r="I17">
+        <v>343.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18">
+        <v>155</v>
+      </c>
+      <c r="C18">
+        <v>29.2</v>
+      </c>
+      <c r="D18">
+        <v>431.5</v>
+      </c>
+      <c r="E18">
+        <v>393.5</v>
+      </c>
+      <c r="F18">
+        <v>337.4</v>
+      </c>
+      <c r="G18">
+        <v>337.4</v>
+      </c>
+      <c r="H18">
+        <v>208.2</v>
+      </c>
+      <c r="I18">
+        <v>337.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19">
+        <v>155</v>
+      </c>
+      <c r="C19">
+        <v>29.2</v>
+      </c>
+      <c r="D19">
+        <v>491.2</v>
+      </c>
+      <c r="E19">
+        <v>446.7</v>
+      </c>
+      <c r="F19">
+        <v>421.5</v>
+      </c>
+      <c r="G19">
+        <v>421.5</v>
+      </c>
+      <c r="H19">
+        <v>261.4</v>
+      </c>
+      <c r="I19">
+        <v>421.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2">
+        <v>285</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E2">
+        <v>53.6</v>
+      </c>
+      <c r="F2">
+        <v>31.2</v>
+      </c>
+      <c r="G2">
+        <v>26.1</v>
+      </c>
+      <c r="H2">
+        <v>-7.9</v>
+      </c>
+      <c r="I2">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3">
+        <v>285</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="E3">
+        <v>61.5</v>
+      </c>
+      <c r="F3">
+        <v>36.6</v>
+      </c>
+      <c r="G3">
+        <v>34.4</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4">
+        <v>285</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>100.1</v>
+      </c>
+      <c r="E4">
+        <v>61.6</v>
+      </c>
+      <c r="F4">
+        <v>39.3</v>
+      </c>
+      <c r="G4">
+        <v>35</v>
+      </c>
+      <c r="H4">
+        <v>0.1</v>
+      </c>
+      <c r="I4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5">
+        <v>277</v>
+      </c>
+      <c r="C5">
+        <v>86.2</v>
+      </c>
+      <c r="D5">
+        <v>100.2</v>
+      </c>
+      <c r="E5">
+        <v>62.3</v>
+      </c>
+      <c r="F5">
+        <v>34</v>
+      </c>
+      <c r="G5">
+        <v>27.8</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6">
+        <v>276</v>
+      </c>
+      <c r="C6">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="D6">
+        <v>100.4</v>
+      </c>
+      <c r="E6">
+        <v>63.2</v>
+      </c>
+      <c r="F6">
+        <v>33</v>
+      </c>
+      <c r="G6">
+        <v>27.6</v>
+      </c>
+      <c r="H6">
+        <v>1.9</v>
+      </c>
+      <c r="I6">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7">
+        <v>285</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="E7">
+        <v>63.3</v>
+      </c>
+      <c r="F7">
+        <v>31.1</v>
+      </c>
+      <c r="G7">
+        <v>27.6</v>
+      </c>
+      <c r="H7">
+        <v>1.8</v>
+      </c>
+      <c r="I7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8">
+        <v>285</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E8">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F8">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>49.5</v>
+      </c>
+      <c r="H8">
+        <v>2.9</v>
+      </c>
+      <c r="I8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9">
+        <v>285</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100.3</v>
+      </c>
+      <c r="E9">
+        <v>65.5</v>
+      </c>
+      <c r="F9">
+        <v>54.7</v>
+      </c>
+      <c r="G9">
+        <v>50.4</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10">
+        <v>285</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>111.2</v>
+      </c>
+      <c r="E10">
+        <v>74.2</v>
+      </c>
+      <c r="F10">
+        <v>53.6</v>
+      </c>
+      <c r="G10">
+        <v>41.7</v>
+      </c>
+      <c r="H10">
+        <v>12.7</v>
+      </c>
+      <c r="I10">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11">
+        <v>277</v>
+      </c>
+      <c r="C11">
+        <v>86.2</v>
+      </c>
+      <c r="D11">
+        <v>116</v>
+      </c>
+      <c r="E11">
+        <v>81.3</v>
+      </c>
+      <c r="F11">
+        <v>63.8</v>
+      </c>
+      <c r="G11">
+        <v>57.9</v>
+      </c>
+      <c r="H11">
+        <v>20</v>
+      </c>
+      <c r="I11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12">
+        <v>252</v>
+      </c>
+      <c r="C12">
+        <v>58.3</v>
+      </c>
+      <c r="D12">
+        <v>146.9</v>
+      </c>
+      <c r="E12">
+        <v>107.2</v>
+      </c>
+      <c r="F12">
+        <v>65.8</v>
+      </c>
+      <c r="G12">
+        <v>59.5</v>
+      </c>
+      <c r="H12">
+        <v>44.7</v>
+      </c>
+      <c r="I12">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13">
+        <v>204</v>
+      </c>
+      <c r="C13">
+        <v>15.6</v>
+      </c>
+      <c r="D13">
+        <v>148.8</v>
+      </c>
+      <c r="E13">
+        <v>110.8</v>
+      </c>
+      <c r="F13">
+        <v>69.8</v>
+      </c>
+      <c r="G13">
+        <v>64.5</v>
+      </c>
+      <c r="H13">
+        <v>33.8</v>
+      </c>
+      <c r="I13">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14">
+        <v>252</v>
+      </c>
+      <c r="C14">
+        <v>58.3</v>
+      </c>
+      <c r="D14">
+        <v>150</v>
+      </c>
+      <c r="E14">
+        <v>111.6</v>
+      </c>
+      <c r="F14">
+        <v>70.7</v>
+      </c>
+      <c r="G14">
+        <v>67.8</v>
+      </c>
+      <c r="H14">
+        <v>49.1</v>
+      </c>
+      <c r="I14">
+        <v>67.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15">
+        <v>252</v>
+      </c>
+      <c r="C15">
+        <v>58.3</v>
+      </c>
+      <c r="D15">
+        <v>153.7</v>
+      </c>
+      <c r="E15">
+        <v>118</v>
+      </c>
+      <c r="F15">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="G15">
+        <v>74.5</v>
+      </c>
+      <c r="H15">
+        <v>55.5</v>
+      </c>
+      <c r="I15">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16">
+        <v>252</v>
+      </c>
+      <c r="C16">
+        <v>58.3</v>
+      </c>
+      <c r="D16">
+        <v>156.7</v>
+      </c>
+      <c r="E16">
+        <v>123.2</v>
+      </c>
+      <c r="F16">
+        <v>77</v>
+      </c>
+      <c r="G16">
+        <v>71.7</v>
+      </c>
+      <c r="H16">
+        <v>60.7</v>
+      </c>
+      <c r="I16">
+        <v>68.40000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B17">
+        <v>172</v>
+      </c>
+      <c r="C17">
+        <v>18.5</v>
+      </c>
+      <c r="D17">
+        <v>248.5</v>
+      </c>
+      <c r="E17">
+        <v>211.4</v>
+      </c>
+      <c r="F17">
+        <v>129.3</v>
+      </c>
+      <c r="G17">
+        <v>124.9</v>
+      </c>
+      <c r="H17">
+        <v>138</v>
+      </c>
+      <c r="I17">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18">
+        <v>204</v>
+      </c>
+      <c r="C18">
+        <v>15.6</v>
+      </c>
+      <c r="D18">
+        <v>319.5</v>
+      </c>
+      <c r="E18">
+        <v>281.4</v>
+      </c>
+      <c r="F18">
+        <v>209.4</v>
+      </c>
+      <c r="G18">
+        <v>202</v>
+      </c>
+      <c r="H18">
+        <v>204.4</v>
+      </c>
+      <c r="I18">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19">
+        <v>204</v>
+      </c>
+      <c r="C19">
+        <v>15.6</v>
+      </c>
+      <c r="D19">
+        <v>332.5</v>
+      </c>
+      <c r="E19">
+        <v>293.4</v>
+      </c>
+      <c r="F19">
+        <v>223.3</v>
+      </c>
+      <c r="G19">
+        <v>217.9</v>
+      </c>
+      <c r="H19">
+        <v>216.4</v>
+      </c>
+      <c r="I19">
+        <v>217.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G13"/>
@@ -1175,16 +2713,16 @@
         <v>338772</v>
       </c>
       <c r="D2">
-        <v>468161</v>
+        <v>477061</v>
       </c>
       <c r="E2">
-        <v>133.4</v>
+        <v>134.6</v>
       </c>
       <c r="F2">
-        <v>-33.4</v>
+        <v>-34.6</v>
       </c>
       <c r="G2">
-        <v>38.2</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1221,16 +2759,16 @@
         <v>338772</v>
       </c>
       <c r="D4">
-        <v>468161</v>
+        <v>477061</v>
       </c>
       <c r="E4">
-        <v>103.6</v>
+        <v>105.6</v>
       </c>
       <c r="F4">
-        <v>-3.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G4">
-        <v>38.2</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1267,16 +2805,16 @@
         <v>338772</v>
       </c>
       <c r="D6">
-        <v>468161</v>
+        <v>477061</v>
       </c>
       <c r="E6">
-        <v>90.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F6">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="G6">
-        <v>38.2</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1313,16 +2851,16 @@
         <v>338772</v>
       </c>
       <c r="D8">
-        <v>468161</v>
+        <v>477061</v>
       </c>
       <c r="E8">
-        <v>58</v>
+        <v>60.9</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>39.1</v>
       </c>
       <c r="G8">
-        <v>38.2</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1359,16 +2897,16 @@
         <v>338772</v>
       </c>
       <c r="D10">
-        <v>468161</v>
+        <v>477061</v>
       </c>
       <c r="E10">
-        <v>45.7</v>
+        <v>46.8</v>
       </c>
       <c r="F10">
-        <v>54.3</v>
+        <v>53.2</v>
       </c>
       <c r="G10">
-        <v>38.2</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1405,16 +2943,16 @@
         <v>338772</v>
       </c>
       <c r="D12">
-        <v>468161</v>
+        <v>477061</v>
       </c>
       <c r="E12">
-        <v>40.7</v>
+        <v>41.6</v>
       </c>
       <c r="F12">
-        <v>59.3</v>
+        <v>58.4</v>
       </c>
       <c r="G12">
-        <v>38.2</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1484,16 +3022,16 @@
         <v>49775</v>
       </c>
       <c r="D2">
-        <v>61432</v>
+        <v>60685</v>
       </c>
       <c r="E2">
-        <v>112.7</v>
+        <v>110.7</v>
       </c>
       <c r="F2">
-        <v>-12.7</v>
+        <v>-10.7</v>
       </c>
       <c r="G2">
-        <v>23.4</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1530,16 +3068,16 @@
         <v>49775</v>
       </c>
       <c r="D4">
-        <v>61432</v>
+        <v>60685</v>
       </c>
       <c r="E4">
-        <v>93</v>
+        <v>90.3</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G4">
-        <v>23.4</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1576,16 +3114,16 @@
         <v>49775</v>
       </c>
       <c r="D6">
-        <v>61432</v>
+        <v>60685</v>
       </c>
       <c r="E6">
-        <v>68.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F6">
-        <v>31.1</v>
+        <v>33.8</v>
       </c>
       <c r="G6">
-        <v>23.4</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1622,16 +3160,16 @@
         <v>49775</v>
       </c>
       <c r="D8">
-        <v>61432</v>
+        <v>60685</v>
       </c>
       <c r="E8">
-        <v>36.7</v>
+        <v>38.2</v>
       </c>
       <c r="F8">
-        <v>63.3</v>
+        <v>61.8</v>
       </c>
       <c r="G8">
-        <v>23.4</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1668,16 +3206,16 @@
         <v>49775</v>
       </c>
       <c r="D10">
-        <v>61432</v>
+        <v>60685</v>
       </c>
       <c r="E10">
-        <v>23.4</v>
+        <v>21.9</v>
       </c>
       <c r="F10">
-        <v>76.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G10">
-        <v>23.4</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1738,7 +3276,7 @@
         <v>8902</v>
       </c>
       <c r="C2">
-        <v>17215</v>
+        <v>17350</v>
       </c>
       <c r="D2">
         <v>10872</v>
@@ -1755,7 +3293,7 @@
         <v>17837</v>
       </c>
       <c r="C3">
-        <v>19899</v>
+        <v>19854</v>
       </c>
       <c r="D3">
         <v>15196</v>
@@ -1772,7 +3310,7 @@
         <v>32283</v>
       </c>
       <c r="C4">
-        <v>31931</v>
+        <v>30963</v>
       </c>
       <c r="D4">
         <v>24832</v>
@@ -1789,7 +3327,7 @@
         <v>17884</v>
       </c>
       <c r="C5">
-        <v>25584</v>
+        <v>24511</v>
       </c>
       <c r="D5">
         <v>20148</v>
@@ -1806,7 +3344,7 @@
         <v>10466</v>
       </c>
       <c r="C6">
-        <v>19914</v>
+        <v>19971</v>
       </c>
       <c r="D6">
         <v>15334</v>
@@ -1823,7 +3361,7 @@
         <v>57426</v>
       </c>
       <c r="C7">
-        <v>52651</v>
+        <v>53628</v>
       </c>
       <c r="D7">
         <v>61890</v>
@@ -1840,7 +3378,7 @@
         <v>17425</v>
       </c>
       <c r="C8">
-        <v>20720</v>
+        <v>20088</v>
       </c>
       <c r="D8">
         <v>14904</v>
@@ -1857,7 +3395,7 @@
         <v>39606</v>
       </c>
       <c r="C9">
-        <v>34004</v>
+        <v>34596</v>
       </c>
       <c r="D9">
         <v>39532</v>
@@ -1874,7 +3412,7 @@
         <v>81442</v>
       </c>
       <c r="C10">
-        <v>79472</v>
+        <v>82483</v>
       </c>
       <c r="D10">
         <v>90486</v>
@@ -1891,7 +3429,7 @@
         <v>20741</v>
       </c>
       <c r="C11">
-        <v>82535</v>
+        <v>82909</v>
       </c>
       <c r="D11">
         <v>92742</v>
@@ -1908,7 +3446,7 @@
         <v>16486</v>
       </c>
       <c r="C12">
-        <v>44896</v>
+        <v>47223</v>
       </c>
       <c r="D12">
         <v>54511</v>
@@ -1925,7 +3463,7 @@
         <v>18274</v>
       </c>
       <c r="C13">
-        <v>39340</v>
+        <v>43485</v>
       </c>
       <c r="D13">
         <v>25245</v>
@@ -2200,7 +3738,7 @@
         <v>144</v>
       </c>
       <c r="D8">
-        <v>69.12</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="E8" t="s">
         <v>154</v>
@@ -2212,16 +3750,16 @@
         <v>13217</v>
       </c>
       <c r="H8">
-        <v>14351.37666666667</v>
+        <v>27922.03018188477</v>
       </c>
       <c r="I8">
-        <v>93.41587854026379</v>
+        <v>167.7153811382979</v>
       </c>
       <c r="J8">
         <v>107.6189755617765</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.9038461538461539</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2337,10 +3875,10 @@
         <v>136</v>
       </c>
       <c r="C12" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D12">
-        <v>92.53</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>158</v>
@@ -2352,16 +3890,16 @@
         <v>9789</v>
       </c>
       <c r="H12">
-        <v>8015</v>
+        <v>7891.35511575502</v>
       </c>
       <c r="I12">
-        <v>86.6687097762795</v>
+        <v>67.09560323166097</v>
       </c>
       <c r="J12">
         <v>86.6687097762795</v>
       </c>
       <c r="K12">
-        <v>0.8653846153846154</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2372,7 +3910,7 @@
         <v>136</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D13">
         <v>91.3</v>
@@ -2442,7 +3980,7 @@
         <v>136</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D15">
         <v>220.35</v>
@@ -2582,7 +4120,7 @@
         <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D19">
         <v>68.05</v>
@@ -2690,7 +4228,7 @@
         <v>139</v>
       </c>
       <c r="D22">
-        <v>59.88</v>
+        <v>58.55</v>
       </c>
       <c r="E22" t="s">
         <v>155</v>
@@ -2702,10 +4240,10 @@
         <v>3111</v>
       </c>
       <c r="H22">
-        <v>4906.637020125613</v>
+        <v>4762.053286579734</v>
       </c>
       <c r="I22">
-        <v>98.33107432925777</v>
+        <v>94.74231086882423</v>
       </c>
       <c r="J22">
         <v>124.1562198649952</v>
@@ -2792,10 +4330,10 @@
         <v>134</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D25">
-        <v>85.34999999999999</v>
+        <v>90.36</v>
       </c>
       <c r="E25" t="s">
         <v>158</v>
@@ -2807,16 +4345,16 @@
         <v>2490</v>
       </c>
       <c r="H25">
-        <v>1847.931508665851</v>
+        <v>1587.340939650308</v>
       </c>
       <c r="I25">
-        <v>79.92731260975975</v>
+        <v>76.86221394912354</v>
       </c>
       <c r="J25">
         <v>83.57429718875503</v>
       </c>
       <c r="K25">
-        <v>0.8846153846153846</v>
+        <v>0.8076923076923077</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2862,7 +4400,7 @@
         <v>134</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D27">
         <v>97.12</v>
@@ -2967,7 +4505,7 @@
         <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D30">
         <v>345.27</v>
@@ -3002,10 +4540,10 @@
         <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D31">
-        <v>79.11</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="E31" t="s">
         <v>159</v>
@@ -3017,16 +4555,16 @@
         <v>1696</v>
       </c>
       <c r="H31">
-        <v>6914.625236685223</v>
+        <v>7135.157341186661</v>
       </c>
       <c r="I31">
-        <v>388.3756978819372</v>
+        <v>388.6112710932782</v>
       </c>
       <c r="J31">
         <v>335.1415094339623</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>0.9615384615384616</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3142,7 +4680,7 @@
         <v>134</v>
       </c>
       <c r="C35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D35">
         <v>245.18</v>
@@ -3247,10 +4785,10 @@
         <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D38">
-        <v>58.3</v>
+        <v>59.43</v>
       </c>
       <c r="E38" t="s">
         <v>155</v>
@@ -3262,16 +4800,16 @@
         <v>1245</v>
       </c>
       <c r="H38">
-        <v>2664.533303150246</v>
+        <v>2546.966096129591</v>
       </c>
       <c r="I38">
-        <v>158.8469533311401</v>
+        <v>148.5465926401393</v>
       </c>
       <c r="J38">
         <v>158.3534136546185</v>
       </c>
       <c r="K38">
-        <v>0.8846153846153846</v>
+        <v>0.9615384615384616</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3282,10 +4820,10 @@
         <v>136</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D39">
-        <v>57.19</v>
+        <v>52.3</v>
       </c>
       <c r="E39" t="s">
         <v>158</v>
@@ -3297,16 +4835,16 @@
         <v>1243</v>
       </c>
       <c r="H39">
-        <v>4663.986481533747</v>
+        <v>4750.753285714286</v>
       </c>
       <c r="I39">
-        <v>335.90484195407</v>
+        <v>333.8218576408842</v>
       </c>
       <c r="J39">
         <v>339.7023330651649</v>
       </c>
       <c r="K39">
-        <v>0.6730769230769231</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3317,7 +4855,7 @@
         <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D40">
         <v>76.66</v>
@@ -3457,31 +4995,31 @@
         <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D44">
-        <v>77.78</v>
+        <v>71.38</v>
       </c>
       <c r="E44" t="s">
         <v>155</v>
       </c>
       <c r="F44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44">
         <v>1012</v>
       </c>
       <c r="H44">
-        <v>924.2012135781631</v>
+        <v>1238.87493046465</v>
       </c>
       <c r="I44">
-        <v>84.40561285463914</v>
+        <v>89.84324239521871</v>
       </c>
       <c r="J44">
         <v>97.13438735177866</v>
       </c>
       <c r="K44">
-        <v>0.9423076923076923</v>
+        <v>0.9038461538461539</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3527,7 +5065,7 @@
         <v>138</v>
       </c>
       <c r="C46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D46">
         <v>85.66</v>
@@ -3600,7 +5138,7 @@
         <v>150</v>
       </c>
       <c r="D48">
-        <v>79.5</v>
+        <v>79.95</v>
       </c>
       <c r="E48" t="s">
         <v>155</v>
@@ -3612,16 +5150,16 @@
         <v>947</v>
       </c>
       <c r="H48">
-        <v>1639.123468136873</v>
+        <v>2091.245826471774</v>
       </c>
       <c r="I48">
-        <v>189.2675225383366</v>
+        <v>220.9271601941474</v>
       </c>
       <c r="J48">
         <v>209.4508975712777</v>
       </c>
       <c r="K48">
-        <v>0.8846153846153846</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -3632,10 +5170,10 @@
         <v>134</v>
       </c>
       <c r="C49" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D49">
-        <v>54.26</v>
+        <v>52.84</v>
       </c>
       <c r="E49" t="s">
         <v>155</v>
@@ -3647,16 +5185,16 @@
         <v>804</v>
       </c>
       <c r="H49">
-        <v>4110.731288675126</v>
+        <v>3475.808011490245</v>
       </c>
       <c r="I49">
-        <v>445.2691184817899</v>
+        <v>391.1602755251934</v>
       </c>
       <c r="J49">
         <v>399.31592039801</v>
       </c>
       <c r="K49">
-        <v>0.5769230769230769</v>
+        <v>0.7884615384615384</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -3667,10 +5205,10 @@
         <v>138</v>
       </c>
       <c r="C50" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D50">
-        <v>61.02</v>
+        <v>58.9</v>
       </c>
       <c r="E50" t="s">
         <v>158</v>
@@ -3682,16 +5220,16 @@
         <v>796</v>
       </c>
       <c r="H50">
-        <v>950.6310672313662</v>
+        <v>813.8938573279206</v>
       </c>
       <c r="I50">
-        <v>105.3672217917222</v>
+        <v>109.0676418708364</v>
       </c>
       <c r="J50">
         <v>103.643216080402</v>
       </c>
       <c r="K50">
-        <v>0.9038461538461539</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3810,7 +5348,7 @@
         <v>139</v>
       </c>
       <c r="D54">
-        <v>125.76</v>
+        <v>119.79</v>
       </c>
       <c r="E54" t="s">
         <v>156</v>
@@ -3822,10 +5360,10 @@
         <v>667</v>
       </c>
       <c r="H54">
-        <v>1007.247725875947</v>
+        <v>864.7136398566406</v>
       </c>
       <c r="I54">
-        <v>108.371743374208</v>
+        <v>88.29728832871488</v>
       </c>
       <c r="J54">
         <v>172.5637181409296</v>
@@ -3845,7 +5383,7 @@
         <v>150</v>
       </c>
       <c r="D55">
-        <v>75.84</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="E55" t="s">
         <v>158</v>
@@ -3857,16 +5395,16 @@
         <v>664</v>
       </c>
       <c r="H55">
-        <v>4438.080417133503</v>
+        <v>4229.220285714287</v>
       </c>
       <c r="I55">
-        <v>594.3781897136957</v>
+        <v>583.5595094664372</v>
       </c>
       <c r="J55">
         <v>603.2379518072289</v>
       </c>
       <c r="K55">
-        <v>0.9423076923076923</v>
+        <v>0.7884615384615384</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -3877,10 +5415,10 @@
         <v>138</v>
       </c>
       <c r="C56" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D56">
-        <v>80.34</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="E56" t="s">
         <v>158</v>
@@ -3892,16 +5430,16 @@
         <v>663</v>
       </c>
       <c r="H56">
-        <v>1663.645369675568</v>
+        <v>1784.868050420168</v>
       </c>
       <c r="I56">
-        <v>287.658395199309</v>
+        <v>281.510606092613</v>
       </c>
       <c r="J56">
         <v>312.4434389140271</v>
       </c>
       <c r="K56">
-        <v>0.9423076923076923</v>
+        <v>0.8846153846153846</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -3912,10 +5450,10 @@
         <v>136</v>
       </c>
       <c r="C57" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D57">
-        <v>51.14</v>
+        <v>48.05</v>
       </c>
       <c r="E57" t="s">
         <v>158</v>
@@ -3927,16 +5465,16 @@
         <v>646</v>
       </c>
       <c r="H57">
-        <v>1139.221555430452</v>
+        <v>1323.935</v>
       </c>
       <c r="I57">
-        <v>113.8015929982542</v>
+        <v>135.7979876160991</v>
       </c>
       <c r="J57">
         <v>123.1424148606811</v>
       </c>
       <c r="K57">
-        <v>0.9423076923076923</v>
+        <v>0.9038461538461539</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -4017,10 +5555,10 @@
         <v>137</v>
       </c>
       <c r="C60" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D60">
-        <v>68.08</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="E60" t="s">
         <v>155</v>
@@ -4032,16 +5570,16 @@
         <v>594</v>
       </c>
       <c r="H60">
-        <v>1183.09448570259</v>
+        <v>1380.135425071833</v>
       </c>
       <c r="I60">
-        <v>202.0973119782931</v>
+        <v>208.4215026150871</v>
       </c>
       <c r="J60">
         <v>261.5319865319865</v>
       </c>
       <c r="K60">
-        <v>0.8076923076923077</v>
+        <v>0.9807692307692307</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4052,10 +5590,10 @@
         <v>135</v>
       </c>
       <c r="C61" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D61">
-        <v>83.09</v>
+        <v>77.56</v>
       </c>
       <c r="E61" t="s">
         <v>155</v>
@@ -4067,16 +5605,16 @@
         <v>580</v>
       </c>
       <c r="H61">
-        <v>1949.718231388993</v>
+        <v>731.8371616095959</v>
       </c>
       <c r="I61">
-        <v>307.2212264799943</v>
+        <v>180.9394708773198</v>
       </c>
       <c r="J61">
         <v>265.5172413793103</v>
       </c>
       <c r="K61">
-        <v>0.9038461538461539</v>
+        <v>0.9423076923076923</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -4160,7 +5698,7 @@
         <v>151</v>
       </c>
       <c r="D64">
-        <v>51.26</v>
+        <v>50.55</v>
       </c>
       <c r="E64" t="s">
         <v>158</v>
@@ -4172,10 +5710,10 @@
         <v>545</v>
       </c>
       <c r="H64">
-        <v>3528.523906888062</v>
+        <v>2812.594175883683</v>
       </c>
       <c r="I64">
-        <v>601.6378265000204</v>
+        <v>467.4987332415897</v>
       </c>
       <c r="J64">
         <v>504.6788990825688</v>
@@ -4227,10 +5765,10 @@
         <v>135</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D66">
-        <v>129</v>
+        <v>139.53</v>
       </c>
       <c r="E66" t="s">
         <v>156</v>
@@ -4242,16 +5780,16 @@
         <v>487</v>
       </c>
       <c r="H66">
-        <v>3764.813510169209</v>
+        <v>2822.880273487364</v>
       </c>
       <c r="I66">
-        <v>711.1557036464114</v>
+        <v>582.8763410186892</v>
       </c>
       <c r="J66">
         <v>669.0965092402464</v>
       </c>
       <c r="K66">
-        <v>0.9807692307692307</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -4297,31 +5835,31 @@
         <v>137</v>
       </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D68">
-        <v>79.42</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="E68" t="s">
         <v>159</v>
       </c>
       <c r="F68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68">
         <v>448</v>
       </c>
       <c r="H68">
-        <v>681.3779272791907</v>
+        <v>567.9013513708513</v>
       </c>
       <c r="I68">
-        <v>115.6864457423686</v>
+        <v>107.2531370786951</v>
       </c>
       <c r="J68">
         <v>132.9241071428571</v>
       </c>
       <c r="K68">
-        <v>0.9230769230769231</v>
+        <v>0.8846153846153846</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -4367,25 +5905,25 @@
         <v>135</v>
       </c>
       <c r="C70" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D70">
-        <v>72.62</v>
+        <v>68.72</v>
       </c>
       <c r="E70" t="s">
         <v>155</v>
       </c>
       <c r="F70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70">
         <v>390</v>
       </c>
       <c r="H70">
-        <v>884.0026966674099</v>
+        <v>804.3667373138608</v>
       </c>
       <c r="I70">
-        <v>168.2056334978381</v>
+        <v>167.7942507444101</v>
       </c>
       <c r="J70">
         <v>177.8205128205128</v>
@@ -4437,7 +5975,7 @@
         <v>134</v>
       </c>
       <c r="C72" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D72">
         <v>107.76</v>
@@ -4542,7 +6080,7 @@
         <v>135</v>
       </c>
       <c r="C75" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D75">
         <v>2722.62</v>
@@ -4612,10 +6150,10 @@
         <v>135</v>
       </c>
       <c r="C77" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D77">
-        <v>75.93000000000001</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="E77" t="s">
         <v>158</v>
@@ -4627,16 +6165,16 @@
         <v>129</v>
       </c>
       <c r="H77">
-        <v>880.9599437822673</v>
+        <v>714.0950688647132</v>
       </c>
       <c r="I77">
-        <v>614.9509707463874</v>
+        <v>499.931032407852</v>
       </c>
       <c r="J77">
         <v>651.5503875968992</v>
       </c>
       <c r="K77">
-        <v>0.9615384615384616</v>
+        <v>0.9807692307692307</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -4647,7 +6185,7 @@
         <v>134</v>
       </c>
       <c r="C78" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D78">
         <v>134.7</v>
@@ -4682,7 +6220,7 @@
         <v>135</v>
       </c>
       <c r="C79" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D79">
         <v>503.67</v>
@@ -4857,7 +6395,7 @@
         <v>138</v>
       </c>
       <c r="C84" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D84">
         <v>828.52</v>
@@ -4927,7 +6465,7 @@
         <v>135</v>
       </c>
       <c r="C86" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D86">
         <v>83.91</v>
@@ -5102,7 +6640,7 @@
         <v>135</v>
       </c>
       <c r="C91" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D91">
         <v>300.77</v>
@@ -5137,7 +6675,7 @@
         <v>138</v>
       </c>
       <c r="C92" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D92">
         <v>160.6</v>
@@ -5207,7 +6745,7 @@
         <v>135</v>
       </c>
       <c r="C94" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D94">
         <v>1634.01</v>
@@ -5347,7 +6885,7 @@
         <v>138</v>
       </c>
       <c r="C98" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D98">
         <v>170.78</v>
@@ -5592,7 +7130,7 @@
         <v>138</v>
       </c>
       <c r="C105" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D105">
         <v>158.16</v>
@@ -5662,7 +7200,7 @@
         <v>134</v>
       </c>
       <c r="C107" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D107">
         <v>132.09</v>
@@ -5872,7 +7410,7 @@
         <v>138</v>
       </c>
       <c r="C113" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D113">
         <v>134.18</v>
@@ -6117,7 +7655,7 @@
         <v>134</v>
       </c>
       <c r="C120" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D120">
         <v>205.97</v>
@@ -6132,10 +7670,10 @@
         <v>7</v>
       </c>
       <c r="H120">
-        <v>82.49138655079953</v>
+        <v>85.02966585934178</v>
       </c>
       <c r="I120">
-        <v>1215.957307762967</v>
+        <v>1240.720386266438</v>
       </c>
       <c r="J120">
         <v>2514.285714285714</v>
@@ -6432,25 +7970,25 @@
         <v>137</v>
       </c>
       <c r="C129" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D129">
-        <v>87.40000000000001</v>
+        <v>86.25</v>
       </c>
       <c r="E129" t="s">
         <v>156</v>
       </c>
       <c r="F129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129">
         <v>3</v>
       </c>
       <c r="H129">
-        <v>2.988376144173057</v>
+        <v>156.3858826319022</v>
       </c>
       <c r="I129">
-        <v>195.7812866722134</v>
+        <v>5158.667662205334</v>
       </c>
       <c r="J129">
         <v>8083.333333333333</v>
@@ -6505,7 +8043,7 @@
         <v>139</v>
       </c>
       <c r="D131">
-        <v>104.95</v>
+        <v>101.55</v>
       </c>
       <c r="E131" t="s">
         <v>158</v>
@@ -6517,10 +8055,10 @@
         <v>3</v>
       </c>
       <c r="H131">
-        <v>4884.482188245913</v>
+        <v>3974.210025507941</v>
       </c>
       <c r="I131">
-        <v>162716.0729415304</v>
+        <v>132373.6675169314</v>
       </c>
       <c r="J131">
         <v>221883.3333333333</v>
@@ -6747,10 +8285,10 @@
         <v>137</v>
       </c>
       <c r="C138" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D138">
-        <v>97.05</v>
+        <v>97.28</v>
       </c>
       <c r="E138" t="s">
         <v>158</v>
@@ -6762,16 +8300,16 @@
         <v>1</v>
       </c>
       <c r="H138">
-        <v>9573.444608207836</v>
+        <v>8471.594207544835</v>
       </c>
       <c r="I138">
-        <v>957244.4608207836</v>
+        <v>847059.4207544834</v>
       </c>
       <c r="J138">
         <v>850800</v>
       </c>
       <c r="K138">
-        <v>0.7884615384615384</v>
+        <v>0.9423076923076923</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -6782,7 +8320,7 @@
         <v>136</v>
       </c>
       <c r="C139" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D139">
         <v>6648.7</v>
@@ -7065,7 +8603,7 @@
         <v>0</v>
       </c>
       <c r="H147">
-        <v>59.74847288869253</v>
+        <v>59.24499890504018</v>
       </c>
       <c r="K147">
         <v>0.3461538461538461</v>
@@ -7137,7 +8675,7 @@
         <v>135</v>
       </c>
       <c r="C150" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D150">
         <v>133.34</v>
@@ -7311,7 +8849,7 @@
         <v>136</v>
       </c>
       <c r="C156" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D156">
         <v>109.22</v>
@@ -7427,7 +8965,7 @@
         <v>138</v>
       </c>
       <c r="C160" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D160">
         <v>172.9</v>
@@ -7572,7 +9110,7 @@
         <v>138</v>
       </c>
       <c r="C165" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D165">
         <v>128.32</v>
@@ -7630,7 +9168,7 @@
         <v>138</v>
       </c>
       <c r="C167" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D167">
         <v>25</v>
@@ -7848,7 +9386,7 @@
         <v>0</v>
       </c>
       <c r="H174">
-        <v>6.252971531512497</v>
+        <v>6.595279306415907</v>
       </c>
       <c r="K174">
         <v>0.6346153846153846</v>
@@ -8500,25 +10038,25 @@
         <v>137</v>
       </c>
       <c r="C197" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D197">
-        <v>100</v>
+        <v>265.24</v>
       </c>
       <c r="E197" t="s">
         <v>156</v>
       </c>
       <c r="F197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G197">
         <v>0</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>614.2366666666667</v>
       </c>
       <c r="K197">
-        <v>1</v>
+        <v>0.7692307692307693</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -8558,7 +10096,7 @@
         <v>135</v>
       </c>
       <c r="C199" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D199">
         <v>175.04</v>
@@ -8811,10 +10349,10 @@
         <v>145</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2">
         <v>13760</v>
@@ -8839,13 +10377,13 @@
         <v>141</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4">
-        <v>84986</v>
+        <v>85566</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8853,13 +10391,13 @@
         <v>142</v>
       </c>
       <c r="B5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>31387</v>
+        <v>32191</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8867,27 +10405,27 @@
         <v>140</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>46478</v>
+        <v>45815</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>13346</v>
+        <v>12412</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8895,116 +10433,116 @@
         <v>139</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>67392</v>
+        <v>71710</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>12253</v>
+        <v>10997</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>5042</v>
+        <v>4611</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>4248</v>
+        <v>5039</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>545</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>545</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>13217</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -9013,7 +10551,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>9789</v>
+        <v>13217</v>
       </c>
     </row>
   </sheetData>
@@ -9023,168 +10561,1437 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>45</v>
       </c>
-      <c r="C2">
-        <v>338772</v>
-      </c>
       <c r="D2">
-        <v>343833</v>
+        <v>424745</v>
       </c>
       <c r="E2">
-        <v>113</v>
+        <v>427115</v>
       </c>
       <c r="F2">
-        <v>-13</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="G2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>2.1</v>
+      </c>
+      <c r="H2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3">
+        <v>424745</v>
+      </c>
+      <c r="E3">
+        <v>435290</v>
+      </c>
+      <c r="F3">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0.4</v>
+      </c>
+      <c r="H3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4">
+        <v>424745</v>
+      </c>
+      <c r="E4">
+        <v>467176</v>
+      </c>
+      <c r="F4">
+        <v>161.2</v>
+      </c>
+      <c r="G4">
+        <v>-61.2</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" t="s">
         <v>50</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="C3">
-        <v>338772</v>
-      </c>
-      <c r="D3">
-        <v>343833</v>
-      </c>
-      <c r="E3">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="F3">
-        <v>9.6</v>
-      </c>
-      <c r="G3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="D5">
+        <v>424745</v>
+      </c>
+      <c r="E5">
+        <v>427115</v>
+      </c>
+      <c r="F5">
+        <v>61.5</v>
+      </c>
+      <c r="G5">
+        <v>38.5</v>
+      </c>
+      <c r="H5">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6">
+        <v>424745</v>
+      </c>
+      <c r="E6">
+        <v>435290</v>
+      </c>
+      <c r="F6">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G6">
+        <v>35.6</v>
+      </c>
+      <c r="H6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7">
+        <v>424745</v>
+      </c>
+      <c r="E7">
+        <v>467176</v>
+      </c>
+      <c r="F7">
+        <v>144.6</v>
+      </c>
+      <c r="G7">
+        <v>-44.6</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" t="s">
         <v>51</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C8" t="s">
         <v>45</v>
       </c>
-      <c r="C4">
-        <v>338772</v>
-      </c>
-      <c r="D4">
-        <v>343833</v>
-      </c>
-      <c r="E4">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="F4">
-        <v>21.9</v>
-      </c>
-      <c r="G4">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
+      <c r="D8">
+        <v>424745</v>
+      </c>
+      <c r="E8">
+        <v>427115</v>
+      </c>
+      <c r="F8">
+        <v>48.9</v>
+      </c>
+      <c r="G8">
+        <v>51.1</v>
+      </c>
+      <c r="H8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9">
+        <v>424745</v>
+      </c>
+      <c r="E9">
+        <v>435290</v>
+      </c>
+      <c r="F9">
+        <v>55.6</v>
+      </c>
+      <c r="G9">
+        <v>44.4</v>
+      </c>
+      <c r="H9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10">
+        <v>424745</v>
+      </c>
+      <c r="E10">
+        <v>467176</v>
+      </c>
+      <c r="F10">
+        <v>136.9</v>
+      </c>
+      <c r="G10">
+        <v>-36.9</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" t="s">
         <v>52</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C11" t="s">
         <v>45</v>
       </c>
-      <c r="C5">
-        <v>338772</v>
-      </c>
-      <c r="D5">
-        <v>343833</v>
-      </c>
-      <c r="E5">
-        <v>54.6</v>
-      </c>
-      <c r="F5">
-        <v>45.4</v>
-      </c>
-      <c r="G5">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="D11">
+        <v>424745</v>
+      </c>
+      <c r="E11">
+        <v>427115</v>
+      </c>
+      <c r="F11">
+        <v>36.6</v>
+      </c>
+      <c r="G11">
+        <v>63.4</v>
+      </c>
+      <c r="H11">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12">
+        <v>424745</v>
+      </c>
+      <c r="E12">
+        <v>435290</v>
+      </c>
+      <c r="F12">
+        <v>54</v>
+      </c>
+      <c r="G12">
+        <v>46</v>
+      </c>
+      <c r="H12">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13">
+        <v>424745</v>
+      </c>
+      <c r="E13">
+        <v>467176</v>
+      </c>
+      <c r="F13">
+        <v>41.2</v>
+      </c>
+      <c r="G13">
+        <v>58.8</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B14" t="s">
         <v>53</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C14" t="s">
         <v>45</v>
       </c>
-      <c r="C6">
-        <v>338772</v>
-      </c>
-      <c r="D6">
-        <v>343833</v>
-      </c>
-      <c r="E6">
-        <v>50.7</v>
-      </c>
-      <c r="F6">
-        <v>49.3</v>
-      </c>
-      <c r="G6">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="D14">
+        <v>424745</v>
+      </c>
+      <c r="E14">
+        <v>427115</v>
+      </c>
+      <c r="F14">
+        <v>34.4</v>
+      </c>
+      <c r="G14">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H14">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D15">
+        <v>424745</v>
+      </c>
+      <c r="E15">
+        <v>435290</v>
+      </c>
+      <c r="F15">
+        <v>49.5</v>
+      </c>
+      <c r="G15">
+        <v>50.5</v>
+      </c>
+      <c r="H15">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16">
+        <v>424745</v>
+      </c>
+      <c r="E16">
+        <v>467176</v>
+      </c>
+      <c r="F16">
+        <v>34.4</v>
+      </c>
+      <c r="G16">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" t="s">
         <v>54</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C17" t="s">
         <v>45</v>
       </c>
-      <c r="C7">
-        <v>338772</v>
-      </c>
-      <c r="D7">
-        <v>343833</v>
-      </c>
-      <c r="E7">
-        <v>31.7</v>
-      </c>
-      <c r="F7">
-        <v>68.3</v>
-      </c>
-      <c r="G7">
-        <v>1.5</v>
+      <c r="D17">
+        <v>424745</v>
+      </c>
+      <c r="E17">
+        <v>427115</v>
+      </c>
+      <c r="F17">
+        <v>28.2</v>
+      </c>
+      <c r="G17">
+        <v>71.8</v>
+      </c>
+      <c r="H17">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
+        <v>168</v>
+      </c>
+      <c r="D18">
+        <v>424745</v>
+      </c>
+      <c r="E18">
+        <v>435290</v>
+      </c>
+      <c r="F18">
+        <v>26</v>
+      </c>
+      <c r="G18">
+        <v>74</v>
+      </c>
+      <c r="H18">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19">
+        <v>424745</v>
+      </c>
+      <c r="E19">
+        <v>467176</v>
+      </c>
+      <c r="F19">
+        <v>31.8</v>
+      </c>
+      <c r="G19">
+        <v>68.2</v>
+      </c>
+      <c r="H19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20">
+        <v>405947</v>
+      </c>
+      <c r="E20">
+        <v>396395</v>
+      </c>
+      <c r="F20">
+        <v>100.9</v>
+      </c>
+      <c r="G20">
+        <v>-0.9</v>
+      </c>
+      <c r="H20">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21">
+        <v>405947</v>
+      </c>
+      <c r="E21">
+        <v>411626</v>
+      </c>
+      <c r="F21">
+        <v>110</v>
+      </c>
+      <c r="G21">
+        <v>-10</v>
+      </c>
+      <c r="H21">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22">
+        <v>405947</v>
+      </c>
+      <c r="E22">
+        <v>456304</v>
+      </c>
+      <c r="F22">
+        <v>162.1</v>
+      </c>
+      <c r="G22">
+        <v>-62.1</v>
+      </c>
+      <c r="H22">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>166</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23">
+        <v>405947</v>
+      </c>
+      <c r="E23">
+        <v>396395</v>
+      </c>
+      <c r="F23">
+        <v>73.7</v>
+      </c>
+      <c r="G23">
+        <v>26.3</v>
+      </c>
+      <c r="H23">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24">
+        <v>405947</v>
+      </c>
+      <c r="E24">
+        <v>411626</v>
+      </c>
+      <c r="F24">
+        <v>80.2</v>
+      </c>
+      <c r="G24">
+        <v>19.8</v>
+      </c>
+      <c r="H24">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25">
+        <v>405947</v>
+      </c>
+      <c r="E25">
+        <v>456304</v>
+      </c>
+      <c r="F25">
+        <v>145</v>
+      </c>
+      <c r="G25">
+        <v>-45</v>
+      </c>
+      <c r="H25">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26">
+        <v>405947</v>
+      </c>
+      <c r="E26">
+        <v>396395</v>
+      </c>
+      <c r="F26">
+        <v>60.4</v>
+      </c>
+      <c r="G26">
+        <v>39.6</v>
+      </c>
+      <c r="H26">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27">
+        <v>405947</v>
+      </c>
+      <c r="E27">
+        <v>411626</v>
+      </c>
+      <c r="F27">
+        <v>70.8</v>
+      </c>
+      <c r="G27">
+        <v>29.2</v>
+      </c>
+      <c r="H27">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28">
+        <v>405947</v>
+      </c>
+      <c r="E28">
+        <v>456304</v>
+      </c>
+      <c r="F28">
+        <v>136.9</v>
+      </c>
+      <c r="G28">
+        <v>-36.9</v>
+      </c>
+      <c r="H28">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29">
+        <v>405947</v>
+      </c>
+      <c r="E29">
+        <v>396395</v>
+      </c>
+      <c r="F29">
+        <v>44.1</v>
+      </c>
+      <c r="G29">
+        <v>55.9</v>
+      </c>
+      <c r="H29">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30">
+        <v>405947</v>
+      </c>
+      <c r="E30">
+        <v>411626</v>
+      </c>
+      <c r="F30">
+        <v>64.2</v>
+      </c>
+      <c r="G30">
+        <v>35.8</v>
+      </c>
+      <c r="H30">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31">
+        <v>405947</v>
+      </c>
+      <c r="E31">
+        <v>456304</v>
+      </c>
+      <c r="F31">
+        <v>40.9</v>
+      </c>
+      <c r="G31">
+        <v>59.1</v>
+      </c>
+      <c r="H31">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32">
+        <v>405947</v>
+      </c>
+      <c r="E32">
+        <v>396395</v>
+      </c>
+      <c r="F32">
+        <v>40.6</v>
+      </c>
+      <c r="G32">
+        <v>59.4</v>
+      </c>
+      <c r="H32">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" t="s">
+        <v>168</v>
+      </c>
+      <c r="D33">
+        <v>405947</v>
+      </c>
+      <c r="E33">
+        <v>411626</v>
+      </c>
+      <c r="F33">
+        <v>56.5</v>
+      </c>
+      <c r="G33">
+        <v>43.5</v>
+      </c>
+      <c r="H33">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>166</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34">
+        <v>405947</v>
+      </c>
+      <c r="E34">
+        <v>456304</v>
+      </c>
+      <c r="F34">
+        <v>33.5</v>
+      </c>
+      <c r="G34">
+        <v>66.5</v>
+      </c>
+      <c r="H34">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>166</v>
+      </c>
+      <c r="B35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35">
+        <v>405947</v>
+      </c>
+      <c r="E35">
+        <v>396395</v>
+      </c>
+      <c r="F35">
+        <v>37.9</v>
+      </c>
+      <c r="G35">
+        <v>62.1</v>
+      </c>
+      <c r="H35">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36">
+        <v>405947</v>
+      </c>
+      <c r="E36">
+        <v>411626</v>
+      </c>
+      <c r="F36">
+        <v>49</v>
+      </c>
+      <c r="G36">
+        <v>51</v>
+      </c>
+      <c r="H36">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>166</v>
+      </c>
+      <c r="B37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37">
+        <v>405947</v>
+      </c>
+      <c r="E37">
+        <v>456304</v>
+      </c>
+      <c r="F37">
+        <v>32.4</v>
+      </c>
+      <c r="G37">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="H37">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38">
+        <v>376430</v>
+      </c>
+      <c r="E38">
+        <v>362708</v>
+      </c>
+      <c r="F38">
+        <v>104.9</v>
+      </c>
+      <c r="G38">
+        <v>-4.9</v>
+      </c>
+      <c r="H38">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
+        <v>168</v>
+      </c>
+      <c r="D39">
+        <v>376430</v>
+      </c>
+      <c r="E39">
+        <v>369850</v>
+      </c>
+      <c r="F39">
+        <v>114.9</v>
+      </c>
+      <c r="G39">
+        <v>-14.9</v>
+      </c>
+      <c r="H39">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>167</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40">
+        <v>376430</v>
+      </c>
+      <c r="E40">
+        <v>441107</v>
+      </c>
+      <c r="F40">
+        <v>164.2</v>
+      </c>
+      <c r="G40">
+        <v>-64.2</v>
+      </c>
+      <c r="H40">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41">
+        <v>376430</v>
+      </c>
+      <c r="E41">
+        <v>362708</v>
+      </c>
+      <c r="F41">
+        <v>78</v>
+      </c>
+      <c r="G41">
+        <v>22</v>
+      </c>
+      <c r="H41">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" t="s">
+        <v>168</v>
+      </c>
+      <c r="D42">
+        <v>376430</v>
+      </c>
+      <c r="E42">
+        <v>369850</v>
+      </c>
+      <c r="F42">
+        <v>85.5</v>
+      </c>
+      <c r="G42">
+        <v>14.5</v>
+      </c>
+      <c r="H42">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43">
+        <v>376430</v>
+      </c>
+      <c r="E43">
+        <v>441107</v>
+      </c>
+      <c r="F43">
+        <v>146.1</v>
+      </c>
+      <c r="G43">
+        <v>-46.1</v>
+      </c>
+      <c r="H43">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44">
+        <v>376430</v>
+      </c>
+      <c r="E44">
+        <v>362708</v>
+      </c>
+      <c r="F44">
+        <v>66.3</v>
+      </c>
+      <c r="G44">
+        <v>33.7</v>
+      </c>
+      <c r="H44">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s">
+        <v>168</v>
+      </c>
+      <c r="D45">
+        <v>376430</v>
+      </c>
+      <c r="E45">
+        <v>369850</v>
+      </c>
+      <c r="F45">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="G45">
+        <v>22.9</v>
+      </c>
+      <c r="H45">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46">
+        <v>376430</v>
+      </c>
+      <c r="E46">
+        <v>441107</v>
+      </c>
+      <c r="F46">
+        <v>137.7</v>
+      </c>
+      <c r="G46">
+        <v>-37.7</v>
+      </c>
+      <c r="H46">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47">
+        <v>376430</v>
+      </c>
+      <c r="E47">
+        <v>362708</v>
+      </c>
+      <c r="F47">
+        <v>44.5</v>
+      </c>
+      <c r="G47">
+        <v>55.5</v>
+      </c>
+      <c r="H47">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48">
+        <v>376430</v>
+      </c>
+      <c r="E48">
+        <v>369850</v>
+      </c>
+      <c r="F48">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="G48">
+        <v>35.4</v>
+      </c>
+      <c r="H48">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>167</v>
+      </c>
+      <c r="B49" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49">
+        <v>376430</v>
+      </c>
+      <c r="E49">
+        <v>441107</v>
+      </c>
+      <c r="F49">
+        <v>40.8</v>
+      </c>
+      <c r="G49">
+        <v>59.2</v>
+      </c>
+      <c r="H49">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>167</v>
+      </c>
+      <c r="B50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" t="s">
+        <v>45</v>
+      </c>
+      <c r="D50">
+        <v>376430</v>
+      </c>
+      <c r="E50">
+        <v>362708</v>
+      </c>
+      <c r="F50">
+        <v>42.2</v>
+      </c>
+      <c r="G50">
+        <v>57.8</v>
+      </c>
+      <c r="H50">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>167</v>
+      </c>
+      <c r="B51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" t="s">
+        <v>168</v>
+      </c>
+      <c r="D51">
+        <v>376430</v>
+      </c>
+      <c r="E51">
+        <v>369850</v>
+      </c>
+      <c r="F51">
+        <v>63</v>
+      </c>
+      <c r="G51">
+        <v>37</v>
+      </c>
+      <c r="H51">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52">
+        <v>376430</v>
+      </c>
+      <c r="E52">
+        <v>441107</v>
+      </c>
+      <c r="F52">
+        <v>32.8</v>
+      </c>
+      <c r="G52">
+        <v>67.2</v>
+      </c>
+      <c r="H52">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53">
+        <v>376430</v>
+      </c>
+      <c r="E53">
+        <v>362708</v>
+      </c>
+      <c r="F53">
+        <v>41.6</v>
+      </c>
+      <c r="G53">
+        <v>58.4</v>
+      </c>
+      <c r="H53">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54">
+        <v>376430</v>
+      </c>
+      <c r="E54">
+        <v>369850</v>
+      </c>
+      <c r="F54">
+        <v>57.7</v>
+      </c>
+      <c r="G54">
+        <v>42.3</v>
+      </c>
+      <c r="H54">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55">
+        <v>376430</v>
+      </c>
+      <c r="E55">
+        <v>441107</v>
+      </c>
+      <c r="F55">
+        <v>31.8</v>
+      </c>
+      <c r="G55">
+        <v>68.2</v>
+      </c>
+      <c r="H55">
+        <v>17.2</v>
       </c>
     </row>
   </sheetData>
@@ -9194,10 +12001,280 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2">
+        <v>8902</v>
+      </c>
+      <c r="C2">
+        <v>17350</v>
+      </c>
+      <c r="D2">
+        <v>18262</v>
+      </c>
+      <c r="E2">
+        <v>10872</v>
+      </c>
+      <c r="F2">
+        <v>9797</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3">
+        <v>18535</v>
+      </c>
+      <c r="C3">
+        <v>12045</v>
+      </c>
+      <c r="D3">
+        <v>9675</v>
+      </c>
+      <c r="E3">
+        <v>15196</v>
+      </c>
+      <c r="F3">
+        <v>19356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4">
+        <v>35867</v>
+      </c>
+      <c r="C4">
+        <v>28328</v>
+      </c>
+      <c r="D4">
+        <v>25312</v>
+      </c>
+      <c r="E4">
+        <v>24832</v>
+      </c>
+      <c r="F4">
+        <v>36945</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5">
+        <v>19562</v>
+      </c>
+      <c r="C5">
+        <v>21679</v>
+      </c>
+      <c r="D5">
+        <v>25666</v>
+      </c>
+      <c r="E5">
+        <v>20148</v>
+      </c>
+      <c r="F5">
+        <v>20265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6">
+        <v>12421</v>
+      </c>
+      <c r="C6">
+        <v>14976</v>
+      </c>
+      <c r="D6">
+        <v>23486</v>
+      </c>
+      <c r="E6">
+        <v>15334</v>
+      </c>
+      <c r="F6">
+        <v>13997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7">
+        <v>63830</v>
+      </c>
+      <c r="C7">
+        <v>36528</v>
+      </c>
+      <c r="D7">
+        <v>17876</v>
+      </c>
+      <c r="E7">
+        <v>61890</v>
+      </c>
+      <c r="F7">
+        <v>69245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8">
+        <v>20818</v>
+      </c>
+      <c r="C8">
+        <v>17699</v>
+      </c>
+      <c r="D8">
+        <v>41218</v>
+      </c>
+      <c r="E8">
+        <v>14904</v>
+      </c>
+      <c r="F8">
+        <v>23225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9">
+        <v>49297</v>
+      </c>
+      <c r="C9">
+        <v>35824</v>
+      </c>
+      <c r="D9">
+        <v>52226</v>
+      </c>
+      <c r="E9">
+        <v>39592</v>
+      </c>
+      <c r="F9">
+        <v>51288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10">
+        <v>108685</v>
+      </c>
+      <c r="C10">
+        <v>94728</v>
+      </c>
+      <c r="D10">
+        <v>74265</v>
+      </c>
+      <c r="E10">
+        <v>90486</v>
+      </c>
+      <c r="F10">
+        <v>110892</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11">
+        <v>32493</v>
+      </c>
+      <c r="C11">
+        <v>71912</v>
+      </c>
+      <c r="D11">
+        <v>66053</v>
+      </c>
+      <c r="E11">
+        <v>92743</v>
+      </c>
+      <c r="F11">
+        <v>33607</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12">
+        <v>26109</v>
+      </c>
+      <c r="C12">
+        <v>38572</v>
+      </c>
+      <c r="D12">
+        <v>47144</v>
+      </c>
+      <c r="E12">
+        <v>54632</v>
+      </c>
+      <c r="F12">
+        <v>26806</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13">
+        <v>28226</v>
+      </c>
+      <c r="C13">
+        <v>37474</v>
+      </c>
+      <c r="D13">
+        <v>34108</v>
+      </c>
+      <c r="E13">
+        <v>26547</v>
+      </c>
+      <c r="F13">
+        <v>28851</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -9219,13 +12296,10 @@
       <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -9234,76 +12308,67 @@
         <v>444274</v>
       </c>
       <c r="D2">
-        <v>343833</v>
+        <v>427115</v>
       </c>
       <c r="E2">
-        <v>49.5</v>
+        <v>37.1</v>
       </c>
       <c r="F2">
-        <v>50.5</v>
+        <v>62.9</v>
       </c>
       <c r="G2">
-        <v>-22.6</v>
-      </c>
-      <c r="H2" t="s">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" t="s">
-        <v>45</v>
       </c>
       <c r="C3">
         <v>444274</v>
       </c>
       <c r="D3">
-        <v>343833</v>
+        <v>435290</v>
       </c>
       <c r="E3">
-        <v>42.7</v>
+        <v>52.2</v>
       </c>
       <c r="F3">
-        <v>57.3</v>
+        <v>47.8</v>
       </c>
       <c r="G3">
-        <v>-22.6</v>
-      </c>
-      <c r="H3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C4">
         <v>444274</v>
       </c>
       <c r="D4">
-        <v>343833</v>
+        <v>467176</v>
       </c>
       <c r="E4">
-        <v>30.2</v>
+        <v>41.3</v>
       </c>
       <c r="F4">
-        <v>69.8</v>
+        <v>58.7</v>
       </c>
       <c r="G4">
-        <v>-22.6</v>
-      </c>
-      <c r="H4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -9312,71 +12377,131 @@
         <v>444274</v>
       </c>
       <c r="D5">
-        <v>468161</v>
+        <v>427115</v>
       </c>
       <c r="E5">
-        <v>39.9</v>
+        <v>34.8</v>
       </c>
       <c r="F5">
-        <v>60.1</v>
+        <v>65.2</v>
       </c>
       <c r="G5">
-        <v>5.4</v>
-      </c>
-      <c r="H5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="C6">
         <v>444274</v>
       </c>
       <c r="D6">
-        <v>468161</v>
+        <v>435290</v>
       </c>
       <c r="E6">
-        <v>38.2</v>
+        <v>47.2</v>
       </c>
       <c r="F6">
-        <v>61.8</v>
+        <v>52.8</v>
       </c>
       <c r="G6">
-        <v>5.4</v>
-      </c>
-      <c r="H6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>444274</v>
       </c>
       <c r="D7">
-        <v>468161</v>
+        <v>467176</v>
       </c>
       <c r="E7">
-        <v>30.8</v>
+        <v>35.1</v>
       </c>
       <c r="F7">
-        <v>69.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G7">
-        <v>5.4</v>
-      </c>
-      <c r="H7" t="s">
-        <v>169</v>
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8">
+        <v>444274</v>
+      </c>
+      <c r="D8">
+        <v>427115</v>
+      </c>
+      <c r="E8">
+        <v>30.3</v>
+      </c>
+      <c r="F8">
+        <v>69.7</v>
+      </c>
+      <c r="G8">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9">
+        <v>444274</v>
+      </c>
+      <c r="D9">
+        <v>435290</v>
+      </c>
+      <c r="E9">
+        <v>28.2</v>
+      </c>
+      <c r="F9">
+        <v>71.8</v>
+      </c>
+      <c r="G9">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10">
+        <v>444274</v>
+      </c>
+      <c r="D10">
+        <v>467176</v>
+      </c>
+      <c r="E10">
+        <v>33</v>
+      </c>
+      <c r="F10">
+        <v>67</v>
+      </c>
+      <c r="G10">
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
